--- a/IMS/src/main/webapp/excelTemplate/SRDetail.xlsx
+++ b/IMS/src/main/webapp/excelTemplate/SRDetail.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\h1\excelTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\innost\Desktop\IMS수정txt\excelTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -64,10 +64,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 작성일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 작성자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -96,14 +92,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SR관리 상세</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>요청사항</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 요청사유</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -201,6 +189,18 @@
   </si>
   <si>
     <t>${asset.eOs}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 등록일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요청내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SR정보 상세</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -601,91 +601,91 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1408,16 +1408,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="A1" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
     </row>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="3" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2"/>
     </row>
@@ -1453,185 +1453,185 @@
     </row>
     <row r="5" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
       <c r="F5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
+        <v>42</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
     </row>
     <row r="6" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
+        <v>12</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
     </row>
     <row r="7" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+        <v>11</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
       <c r="F7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
+      <c r="G7" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
     </row>
     <row r="8" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
+      <c r="A8" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
     </row>
     <row r="9" spans="1:10" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
+      <c r="A9" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
     </row>
     <row r="10" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
+        <v>17</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
       <c r="F11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
+        <v>15</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
     </row>
     <row r="12" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
+        <v>14</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
       <c r="F12" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
+        <v>13</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
     </row>
     <row r="13" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="19"/>
+      <c r="A14" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="36"/>
     </row>
     <row r="15" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="20"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="22" t="s">
+      <c r="A15" s="13"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="17"/>
+    </row>
+    <row r="16" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="13"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="24"/>
-    </row>
-    <row r="16" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="20"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="26"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="19"/>
     </row>
     <row r="17" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="20"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="26"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="19"/>
     </row>
     <row r="19" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
@@ -1651,88 +1651,88 @@
       <c r="J20" s="6"/>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="27" t="s">
+      <c r="C21" s="37"/>
+      <c r="D21" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="28"/>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="37"/>
+      <c r="G21" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H21" s="27" t="s">
+      <c r="H21" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="27" t="s">
+      <c r="I21" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="J21" s="27" t="s">
+      <c r="J21" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="39"/>
+      <c r="A22" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="27"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="31"/>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="33" t="s">
+      <c r="A23" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="19"/>
+      <c r="G23" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="34" t="s">
+      <c r="H23" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="I23" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="26"/>
-      <c r="G23" s="34" t="s">
+      <c r="J23" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="H23" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="J23" s="40" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="41"/>
+      <c r="A24" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="29"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="33"/>
     </row>
     <row r="25" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
